--- a/output/(山本)目的適合性_目的明示性_再構成.xlsx
+++ b/output/(山本)目的適合性_目的明示性_再構成.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26.13" customWidth="1" min="1" max="1"/>
@@ -461,90 +461,90 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>文書の冒頭または「はじめに」等の項目において、職種、役割、組織上の立場などの観点から、主たる読者が誰であるかを明記している。</t>
+          <t>対象文書の冒頭章または前提条件の章において、想定読者の職種、プロジェクトにおける役割、および理解に必須となる技術的知識を明記している。</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】読み手の役割に関する記述が曖昧で、想定読者が特定できない。
-→【適合例】本設計書の主な読み手は、プロジェクトの実装担当者および単体テストの設計者とする。</t>
+【非適合例】本書はシステムの仕様をまとめたものである。（非適合の理由：想定読者の職種や前提となる技術的知識が記述されていないため。）
+→【適合例】本書の想定読者は、本システムのバックエンドAPIを実装する開発エンジニアである。RESTful API設計の基本概念および認証基盤の仕組みを理解していることを前提とする。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>文書の読み手（属性や特性）を記述している</t>
+          <t>文書の読み手の範囲（提出先,配布先,開示範囲）を記述している</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>文書の内容を正しく理解し記述事項を遂行するために、読み手に求められる前提知識、技術スキル、または実務経験の具体的なレベルを客観的指標に基づき明記している。</t>
+          <t>文書管理情報または改訂履歴のページにおいて、文書の提出先組織、配布対象となるチーム、および情報の開示範囲（社外秘、プロジェクト内限定など）を明記している。</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】読み手に必要な技術水準や前提知識に関する記述が欠落している。
-→【適合例】本手順書の読み手は、Linuxの基本操作および標準的なSQLクエリによるデータ抽出が可能な知識を有していることを前提とする。</t>
+【非適合例】本書はプロジェクト計画書であり、フェーズごとの成果物およびスケジュールを記載する。（非適合の理由：提出先組織、配布対象チーム、および情報開示の範囲が記述されていないため。）
+→【適合例】本書の提出先はシステム企画部であり、配布範囲は開発ベンダーのプロジェクトメンバーのみとする。また、本ドキュメントの取扱いは「社外秘」とする。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>文書の読み手の範囲（提出先,配布先,開示範囲）を記述している</t>
+          <t>文書の適用範囲を記述している</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>情報セキュリティ方針や文書の機密性に基づき、当該文書を配布または開示する組織、部門、役職、および閲覧権限の範囲を具体的に明記している。</t>
+          <t>適用範囲を規定する章において、対象となるシステムコンポーネント、業務領域、および開発スコープの境界線（対象外とする範囲を含む）を明記している。</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】プロジェクト計画書に、配布先や開示可能なステークホルダーの範囲が記載されていない。
-→【適合例】本プロジェクト計画書の配布先は、運営委員会（ステアリングコミッティ）のメンバーおよび各作業班のリーダーに限定する。</t>
+【非適合例】本要件定義書において、顧客の要望に基づく機能要件を定義する。（非適合の理由：要件定義の対象となる具体的なシステムコンポーネントや開発スコープの境界線が記述されていないため。）
+→【適合例】本要件定義書の適用範囲は、次期ECサイト構築プロジェクトにおける「フェーズ1（商品検索およびカート機能）」に限定する。決済連携フェーズは本要件の対象外とする。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>文書の適用範囲を記述している</t>
+          <t>文書の目的を記述している</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>当該文書が対象とするシステム、業務プロセス、または開発工程の境界を定義し、対象に含まれる範囲（スコープ）と対象外とする範囲（アウトオブスコープ）を峻別して明記している。</t>
+          <t>文書の目的を記載する章において、文書の作成意図、および後続工程における利用目的（レビュアーの確認観点や実装者の参照基準など）を明記している。</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】システム要件定義書において、対象業務の境界が不明確なまま要件が記述されている。
-→【適合例】本システムの適用範囲は「受注管理」および「在庫引当」の業務に限定し、外部倉庫との「配送連携」は本要件定義の対象外とする。</t>
+【非適合例】本詳細設計書には、ログイン機能に関する仕様を記述する。（非適合の理由：文書の作成意図や後続工程における利用目的が記述されていないため。）
+→【適合例】本詳細設計書の目的は、基本設計書で定義された機能要件を満たすための内部構造を定義し、実装担当者がコーディングを行うための仕様を提示することである。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>文書の目的を記述している</t>
+          <t>文書の目的を達成するために必要な項目を記述している</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>文書を作成する背景や意図、解決すべき課題を定義し、その文書がシステム開発ライフサイクルやプロジェクト運営において果たすべき役割を明記している。</t>
+          <t>要求仕様書において、要求の妥当性を検証するために必要な情報として、上位目的（ビジネス上の課題解決など）および開発スコープを専用の章に明記している。</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】ソフトウェア設計書に、文書作成の目的や設計の基本方針が記述されていない。
-→【適合例】本ソフトウェア設計書の目的は、要件定義書で合意された機能要件を具体的なモジュール構造およびデータ構造へと変換し、開発担当者へ実装指示を行うことである。</t>
+【非適合例】本要求仕様書では、システムの具体的な機能および画面遷移について記述する。（非適合の理由：要求を定義する上で前提となるビジネス上の課題解決などの上位目的が記述されていないため。）
+→【適合例】本要求仕様書の第1章には、業務効率化による残業時間20%削減という「開発の目的」、および顧客管理システム改修という「開発のスコープ」を明記している。</t>
         </is>
       </c>
     </row>
@@ -556,14 +556,14 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>要求仕様書において、システム化に至った経緯、解決したいビジネス上の課題、および開発作業の対象となる具体的な範囲を、達成すべきゴールとして明記している。</t>
+          <t>要件定義書において、システムの網羅的な品質目標を担保するため、機能要件とは独立した非機能要件（性能、セキュリティ、可用性など）の章を設けている。</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】要求仕様書に、開発によって解決すべきビジネス上の目的が明示されていない。
-→【適合例】本開発の目的は、現行のレガシーシステムを刷新し、受注処理のリードタイムを現行の50%以下に短縮することである。</t>
+【非適合例】本要件定義書の要件一覧には、業務フローに基づく機能要件のみを記述する。（非適合の理由：システムの品質目標を担保するために必要な非機能要件の章が欠落しているため。）
+→【適合例】本要件定義書には、第3章に機能要件を記述し、第4章にシステム基盤の品質目標を定義する非機能要件（性能、セキュリティ、可用性）の章を設けている。</t>
         </is>
       </c>
     </row>
@@ -575,14 +575,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>要求仕様書において、機能要件だけでなく、システムの品質、運用性、継続性を担保するために不可欠な非機能要求（性能、信頼性、セキュリティ等）を定義する独立した章または項を設けている。</t>
+          <t>基本設計書において、設計の妥当性を示すため、アーキテクチャ選定の背景および採用技術の技術的根拠を基本方針の章に明記している。</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】要求仕様書に、非機能要求（性能やセキュリティ等）を定義する項目が存在しない。
-→【適合例】第5章に「非機能要求仕様」の項を設け、目標レスポンスタイムおよび同時接続数に関する制約を記述している。</t>
+【非適合例】本システムのデータベースにはPostgreSQLを採用し、テーブル定義を進める。（非適合の理由：採用技術の技術的根拠やアーキテクチャ選定の背景が記述されていないため。）
+→【適合例】基本設計書の基本方針の章に、設計の目的として「高可用性の実現」を掲げ、これを達成するためにPostgreSQLのクラスタリング構成を採用した技術的根拠を記述している。</t>
         </is>
       </c>
     </row>
@@ -594,14 +594,14 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>設計書において、単なる機能の実装方法だけでなく、特定のアルゴリズムや構成を採用した技術的根拠、および設計上の制約事項を意図として明記している。</t>
+          <t>方式設計書において、保守性および拡張性を確保するため、将来的な機能追加や改訂開発を想定した設計方針を明記している。</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】設計書に、その設計を採用した根拠や意図を記述する項目が存在しない。
-→【適合例】本設計の目的は、ピーク時のトラフィック負荷を分散し、システムの応答性を一定に保つためのアーキテクチャを定義することである。</t>
+【非適合例】ユーザー認証機能は、現在の要求仕様に基づきIDおよびパスワードによる単一認証で実装する。（非適合の理由：将来的な拡張性を確保するための設計方針が記述されていないため。）
+→【適合例】将来の改訂開発（SaaS型のマルチテナント化）を想定した設計方針として、データベースの論理設計においてテナントIDを複合主キーとして持たせる旨を記述している。</t>
         </is>
       </c>
     </row>
@@ -613,36 +613,14 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>将来的なシステムの拡張、保守、または機能改訂を円滑に行うことを目的として、ソースコードの可読性向上やモジュール結合度の低減など、拡張性に関する設計方針を明記している。</t>
+          <t>議事録において、合意形成のトレーサビリティを確保するため、開催日、参加者、議題、決定事項、および次回のアクションアイテムを記載する項目を設けている。</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】将来の保守性や改訂開発を想定した、設計上の考慮事項が一切記述されていない。
-→【適合例】本システムは将来的な決済手段の追加を想定し、決済処理を独立したモジュールとして設計することで、改訂時の影響範囲を最小化する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>文書の目的を達成するために必要な項目を記述している</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>議事録において、合意形成の証跡としての役割を果たすため、開催日時、場所、出席者、議題、決定事項、および継続検討課題（ToDo）を網羅して記述している。</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>★新規追加
-【非適合例】議事録に開催日や出席者が記載されておらず、発言の断片のみが記録されている。
-→【適合例】開催日：2024/03/25
-出席者：A社（田中）、B社（佐藤）
-議題：API仕様の最終確定
-決定事項：案Aを採用し、次週月曜までにI/F仕様書を更新する。</t>
+【非適合例】前回のミーティングでは、新機能の方向性について話し合い、A案を採用することに意見が一致した。（非適合の理由：合意形成のトレーサビリティを確保するための決定事項やアクションアイテムを記載する項目が欠落しているため。）
+→【適合例】議事録の標準フォーマットとして、会議の開催日、参加者、議題に加え、決定事項および次回のアクションアイテムを明記する項目を設けている。</t>
         </is>
       </c>
     </row>
